--- a/BWI/bestwine_output/bestwine_Réunion.xlsx
+++ b/BWI/bestwine_output/bestwine_Réunion.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA40"/>
+  <dimension ref="A1:AA41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -4608,6 +4608,99 @@
       <c r="Z40" s="2" t="inlineStr"/>
       <c r="AA40" s="2" t="inlineStr"/>
     </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>La Bourbonnaise De Vins Eurl</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>La Bourbonnaise De Vins Eurl</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>52559</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>Réunion</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>Saint Andre</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>Saint-Benoît, Canton de Saint-André-2</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>392 Rue Andropolis</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>97440</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>https://www.lbv.re</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr"/>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>direction@lbv.re</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr"/>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>1996</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t>40418115800043</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr"/>
+      <c r="V41" s="2" t="inlineStr"/>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>Philippe Michelas</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr"/>
+      <c r="Z41" s="2" t="inlineStr"/>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/philippe-michelas-73090615b/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
